--- a/output/pdf_financials_xlsx/QRO.xlsx
+++ b/output/pdf_financials_xlsx/QRO.xlsx
@@ -5643,46 +5643,46 @@
         <v>0.617579</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.617579</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.617579</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.617579</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.617579</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.617579</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.617579</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.789228</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.835996</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.867599</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.303845</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.303845</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.303845</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>1.334822</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>1.374467</v>
       </c>
     </row>
     <row r="93">
@@ -7062,13 +7062,13 @@
         <v>0.060953</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0.218416</v>
+        <v>0.117616</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0.162768</v>
+        <v>0.09056400000000001</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0.158276</v>
+        <v>0.147728</v>
       </c>
     </row>
     <row r="119">
@@ -9276,7 +9276,11 @@
           <t>Share-based payment reserve (Note 11)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -10110,7 +10114,11 @@
           <t>Share-based payment reserve (Note 12)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -11996,7 +12004,11 @@
           <t>Share-based payments reserve 9</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -12772,7 +12784,11 @@
           <t>Share-based payments reserve 9</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -13718,7 +13734,11 @@
           <t>Share-based payments reserve 7</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -14104,7 +14124,11 @@
           <t>Share-based payments reserve 9</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -14972,7 +14996,11 @@
           <t>Share-based payments reserve 10</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -15650,7 +15678,11 @@
           <t>Share-based payments reserve 11</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -16528,7 +16560,11 @@
           <t>Share-based payments reserve 11</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -18566,7 +18602,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/QRO.xlsx
+++ b/output/pdf_financials_xlsx/QRO.xlsx
@@ -919,22 +919,22 @@
         <v>0.219793</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.593808</v>
+        <v>0.670753</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.01322</v>
+        <v>0.814196</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.74405</v>
+        <v>0.4058</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.262491</v>
+        <v>0.365719</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.231216</v>
+        <v>0.326915</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.149755</v>
+        <v>0.229574</v>
       </c>
     </row>
     <row r="11">
@@ -974,22 +974,22 @@
         <v>-0.219793</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.593808</v>
+        <v>-0.670753</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.01322</v>
+        <v>-0.814196</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.74405</v>
+        <v>-0.4058</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-0.262491</v>
+        <v>-0.365719</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.231216</v>
+        <v>-0.326915</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-0.149755</v>
+        <v>-0.229574</v>
       </c>
     </row>
     <row r="12">
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.01586</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.003112</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1014,7 +1014,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>1.2e-05</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.205331</v>
+        <v>-0.221191</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-3.057025</v>
+        <v>-3.060137</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.299426</v>
@@ -1945,7 +1945,7 @@
         <v>-0.128142</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.07298200000000001</v>
+        <v>-0.072994</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-0.03351</v>
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.205331</v>
+        <v>-0.221191</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.057025</v>
+        <v>-3.060137</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.295665</v>
@@ -2055,7 +2055,7 @@
         <v>-0.12585</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.071274</v>
+        <v>-0.071286</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-0.032233</v>
@@ -2331,52 +2331,52 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.020391</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.914023</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.451199</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.234127</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.076332</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.022913</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.003512</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.11657</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.522702</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.161105</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.812187</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.450445</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.521629</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.162781</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.094273</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.00731</v>
       </c>
     </row>
     <row r="35">
@@ -2441,52 +2441,52 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.020391</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.914023</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.451199</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.234127</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.076332</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.022913</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.003512</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.11657</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.522702</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.161105</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.812187</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.450445</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.521629</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.154613</v>
+        <v>0.317394</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.125387</v>
+        <v>0.21966</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.090387</v>
+        <v>0.09769700000000001</v>
       </c>
     </row>
     <row r="37">
@@ -3101,52 +3101,52 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.02549</v>
+        <v>0.005099</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.919122</v>
+        <v>0.005099</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.480232</v>
+        <v>0.029033</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.245929</v>
+        <v>0.011802</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.077532</v>
+        <v>0.0012</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.022913</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.005219</v>
+        <v>0.001707</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.11657</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.535702</v>
+        <v>0.013</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.17639</v>
+        <v>0.015285</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.910738</v>
+        <v>0.098551</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.450445</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.521629</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.162781</v>
+        <v>0</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.094273</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.00731</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -25546,7 +25546,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -25600,22 +25600,22 @@
         </is>
       </c>
       <c r="O186" s="5" t="n">
-        <v>-0.670753</v>
+        <v>0.670753</v>
       </c>
       <c r="P186" s="5" t="n">
-        <v>-0.814196</v>
+        <v>0.814196</v>
       </c>
       <c r="Q186" s="5" t="n">
-        <v>-0.4058</v>
+        <v>0.4058</v>
       </c>
       <c r="R186" s="5" t="n">
-        <v>-0.365719</v>
+        <v>0.365719</v>
       </c>
       <c r="S186" s="5" t="n">
-        <v>-0.326915</v>
+        <v>0.326915</v>
       </c>
       <c r="T186" s="5" t="n">
-        <v>-0.229574</v>
+        <v>0.229574</v>
       </c>
     </row>
     <row r="187">
@@ -33114,7 +33114,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E267" s="5" t="n">

--- a/output/pdf_financials_xlsx/QRO.xlsx
+++ b/output/pdf_financials_xlsx/QRO.xlsx
@@ -4192,46 +4192,46 @@
         <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.027325</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.0129</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.0115</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.009606999999999999</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.043339</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.02775</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.066</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.174505</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.064</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.08500000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -4247,46 +4247,46 @@
         <v>0.158613</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0.043622</v>
+        <v>0.066622</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0.0467</v>
+        <v>0.07402499999999999</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.022934</v>
+        <v>0.035834</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.031552</v>
+        <v>0.043052</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0.030298</v>
+        <v>0.039905</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.076775</v>
+        <v>0.120114</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.070775</v>
+        <v>0.098525</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0.089641</v>
+        <v>0.172641</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.105151</v>
+        <v>0.171151</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>0.229605</v>
+        <v>0.40411</v>
       </c>
       <c r="N68" s="3" t="n">
-        <v>0.092964</v>
+        <v>0.156964</v>
       </c>
       <c r="O68" s="3" t="n">
-        <v>0.104075</v>
+        <v>0.168075</v>
       </c>
       <c r="P68" s="3" t="n">
-        <v>0.085601</v>
+        <v>0.170601</v>
       </c>
       <c r="Q68" s="3" t="n">
-        <v>0.104161</v>
+        <v>0.189161</v>
       </c>
     </row>
     <row r="69">
@@ -4656,22 +4656,22 @@
         <v>0</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.006313</v>
+        <v>0</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.103613</v>
+        <v>0</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.013562</v>
+        <v>0</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>0.008403000000000001</v>
+        <v>0</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>0.008403000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>0.008403000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -6638,13 +6638,13 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000886</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001969</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002358</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
@@ -6668,10 +6668,10 @@
         <v>0</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002183</v>
       </c>
       <c r="M111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001717</v>
       </c>
       <c r="N111" s="3" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>0.09128500000000001</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>0.024655</v>
       </c>
     </row>
     <row r="116">
@@ -7935,13 +7935,13 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000886</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001969</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002358</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
@@ -7965,10 +7965,10 @@
         <v>0</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002183</v>
       </c>
       <c r="M134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001717</v>
       </c>
       <c r="N134" s="3" t="n">
         <v>0</v>
@@ -7990,13 +7990,13 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.210383</v>
+        <v>-0.211269</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.191263</v>
+        <v>-0.193232</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-0.242835</v>
+        <v>-0.245193</v>
       </c>
       <c r="E135" s="3" t="n">
         <v>-0.210097</v>
@@ -8020,10 +8020,10 @@
         <v>-0.136269</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-0.7393</v>
+        <v>-0.741483</v>
       </c>
       <c r="M135" s="3" t="n">
-        <v>-0.326169</v>
+        <v>-0.327886</v>
       </c>
       <c r="N135" s="3" t="n">
         <v>-0.5403250000000001</v>
@@ -18790,7 +18790,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -20998,7 +21002,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -23960,7 +23968,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E169" s="5" t="n">
         <v>-0.000886</v>
       </c>
